--- a/Pravartiya/test/SEBI_Board_Meetings.xlsx
+++ b/Pravartiya/test/SEBI_Board_Meetings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="32">
   <si>
     <t>Year</t>
   </si>
@@ -109,118 +109,7 @@
     <t>https://www.sebi.gov.in/sebi_data/meetingfiles/apr-2026/1775541390162_2.pdf</t>
   </si>
   <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>Monday 23 rd March</t>
-  </si>
-  <si>
-    <t>Proposed amendments to the ‘Fit and Proper Person’ criteria specified under Schedule II of the Securities and Exchange Board of India (Intermediaries) Regulations, 2008 and Addendum.</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/apr-2026/1776078876032_1.pdf</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782284355875_2.pdf</t>
-  </si>
-  <si>
-    <t>Review of minimum value of investment by individual investors in Social Impact Fund under SEBI (Alternative Investment Funds) Regulations, 2012. Agenda</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/apr-2026/1775545254714_1.pdf</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782284450716_2.pdf</t>
-  </si>
-  <si>
-    <t>Flexibility to AIFs in winding up of scheme and surrendering of registration.</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/apr-2026/1775554233126_1.pdf</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782284468290_2.pdf</t>
-  </si>
-  <si>
-    <t>Proposal to permit net settlement of funds for transactions done by Foreign Portfolio Investor.</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/apr-2026/1775802683050_1.pdf</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782284485135_2.pdf</t>
-  </si>
-  <si>
-    <t>Measures towards Ease of Doing Business for Infrastructure Investment trusts and Real Estate Investment Trusts.</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/apr-2026/1775545313668_1.pdf</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782284501437_2.pdf</t>
-  </si>
-  <si>
-    <t>Friday 19 th June</t>
-  </si>
-  <si>
-    <t>Justice (Retd.) R.M. Lodha Committee (In the matter of PACL Ltd.) – Developments made by the Committee</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jul-2026/1782895902429_1.pdf</t>
-  </si>
-  <si>
-    <t>Proposal for Payment of SEBI FPI and FVCI Registration &amp; Related Fees in INR and Proposal for capturing date of Birth/Incorporation of FPI in the FPI Registration Certificate</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jul-2026/1782896379967_1.pdf</t>
-  </si>
-  <si>
-    <t>Proposal for revision of frequency for collecting Custodian fees</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782821373894_1.pdf</t>
-  </si>
-  <si>
-    <t>Transfer of funds, administration &amp; management of Capacity Building Fund (CBF) to Section 8 Company in respect of Social Stock Exchange</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782819875076_1.pdf</t>
-  </si>
-  <si>
-    <t>Re-introduction of Open Market Buy-Back through Stock Exchange and review of the SEBI (Buy-Back of Securities) Regulations, 2018</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782819500272_1.pdf</t>
-  </si>
-  <si>
-    <t>Amendments to the Securities and Exchange Board of India (Issue and Listing of Securitised Debt Instruments and Security Receipts) Regulations, 2008</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782820168413_1.pdf</t>
-  </si>
-  <si>
-    <t>‘Green-Channel: AIF Rollout Upon Document Acknowledgement’ (GARUDA) Mechanism for Processing of Placement Memorandum of Alternative Investment Funds (AIFs) filed with SEBI</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782820346489_1.pdf</t>
-  </si>
-  <si>
-    <t>Simplifying and standardising the framework for transmission of securities</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jul-2026/1782895959766_1.pdf</t>
-  </si>
-  <si>
-    <t>Utilization of intraday borrowing lines by Mutual Funds</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jun-2026/1782819939164_1.pdf</t>
-  </si>
-  <si>
-    <t>Review of SEBI (Issue and Listing of Municipal Debt Securities) Regulations, 2015</t>
-  </si>
-  <si>
-    <t>https://www.sebi.gov.in/sebi_data/meetingfiles/jul-2026/1782896627806_1.pdf</t>
+    <t/>
   </si>
 </sst>
 </file>
@@ -228,7 +117,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,13 +127,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -291,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -299,14 +182,20 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -616,11 +505,11 @@
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="26.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="84.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="27.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="16.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="26.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="84.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="27.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="16.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -691,7 +580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -708,7 +597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -725,7 +614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -742,7 +631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -759,7 +648,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -776,238 +665,238 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
-      <c r="A10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
-      <c r="A13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
-      <c r="A15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>50</v>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>52</v>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
-      <c r="A17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>54</v>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>56</v>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
-      <c r="A19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>58</v>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
-      <c r="A20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>60</v>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
-      <c r="A21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>62</v>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>64</v>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
-      <c r="A23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>66</v>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
-      <c r="A24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>68</v>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E24" s="4"/>
     </row>
